--- a/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="11670"/>
+    <workbookView windowWidth="23520" windowHeight="11670"/>
   </bookViews>
   <sheets>
     <sheet name="ExternalDisplayProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>#</t>
   </si>
@@ -52,6 +52,15 @@
     <t>名字</t>
   </si>
   <si>
+    <t>部位</t>
+  </si>
+  <si>
+    <t>体型</t>
+  </si>
+  <si>
+    <t>是否看身材体型</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -65,6 +74,15 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>PartKey</t>
+  </si>
+  <si>
+    <t>BodyType</t>
+  </si>
+  <si>
+    <t>NeedBodyType</t>
   </si>
   <si>
     <t>Desc</t>
@@ -1400,8 +1418,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:H61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="C2:K61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
@@ -1409,15 +1427,17 @@
     <col min="6" max="6" width="15.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="12.125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8">
+    <row r="2" spans="3:11">
       <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8">
+    <row r="3" spans="3:11">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1436,48 +1456,75 @@
       <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="3:8">
+      <c r="I3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8">
+        <v>14</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11">
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:8">
+        <v>18</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:11">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -1491,13 +1538,22 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:8">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:11">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -1511,13 +1567,22 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:8">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:11">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -1531,13 +1596,22 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:8">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:11">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -1551,13 +1625,22 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -1571,13 +1654,22 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -1591,13 +1683,22 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -1611,13 +1712,22 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8">
+        <v>32</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -1631,13 +1741,22 @@
         <v>2</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8">
+        <v>34</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="3:11">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -1651,13 +1770,22 @@
         <v>2</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="3:8">
+        <v>36</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="3:11">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -1671,13 +1799,22 @@
         <v>2</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="3:8">
+        <v>38</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="3:11">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -1691,13 +1828,22 @@
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="3:8">
+        <v>40</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="28.5" spans="3:11">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
@@ -1711,13 +1857,22 @@
         <v>3</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="3:8">
+        <v>42</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="28.5" spans="3:11">
       <c r="C18" s="1">
         <v>1013</v>
       </c>
@@ -1731,13 +1886,22 @@
         <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="3:8">
+        <v>44</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="28.5" spans="3:11">
       <c r="C19" s="1">
         <v>1014</v>
       </c>
@@ -1751,13 +1915,22 @@
         <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="3:8">
+        <v>46</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="28.5" spans="3:11">
       <c r="C20" s="1">
         <v>1015</v>
       </c>
@@ -1771,13 +1944,22 @@
         <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="3:8">
+        <v>48</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="28.5" spans="3:11">
       <c r="C21" s="1">
         <v>1016</v>
       </c>
@@ -1791,13 +1973,22 @@
         <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="3:8">
+        <v>50</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="28.5" spans="3:11">
       <c r="C22" s="1">
         <v>1017</v>
       </c>
@@ -1811,13 +2002,22 @@
         <v>3</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="3:8">
+        <v>52</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="28.5" spans="3:11">
       <c r="C23" s="1">
         <v>1018</v>
       </c>
@@ -1831,13 +2031,22 @@
         <v>3</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="3:8">
+        <v>54</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="3:11">
       <c r="C24" s="1">
         <v>1019</v>
       </c>
@@ -1851,13 +2060,22 @@
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="3:8">
+        <v>56</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="3:11">
       <c r="C25" s="1">
         <v>1020</v>
       </c>
@@ -1871,13 +2089,22 @@
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="3:8">
+        <v>58</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="3:11">
       <c r="C26" s="1">
         <v>1021</v>
       </c>
@@ -1891,13 +2118,22 @@
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="3:8">
+        <v>60</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="3:11">
       <c r="C27" s="1">
         <v>1022</v>
       </c>
@@ -1911,13 +2147,22 @@
         <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="3:8">
+        <v>62</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="3:11">
       <c r="C28" s="1">
         <v>1023</v>
       </c>
@@ -1931,13 +2176,22 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="3:8">
+        <v>64</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="3:11">
       <c r="C29" s="1">
         <v>1024</v>
       </c>
@@ -1951,13 +2205,22 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="3:8">
+        <v>66</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="3:11">
       <c r="C30" s="1">
         <v>1025</v>
       </c>
@@ -1971,13 +2234,22 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="3:8">
+        <v>68</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="3:11">
       <c r="C31" s="1">
         <v>1026</v>
       </c>
@@ -1991,13 +2263,22 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="3:8">
+        <v>70</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="3:11">
       <c r="C32" s="1">
         <v>1027</v>
       </c>
@@ -2011,13 +2292,22 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="3:8">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1">
+        <v>2</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="3:11">
       <c r="C33" s="1">
         <v>1028</v>
       </c>
@@ -2031,13 +2321,22 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="3:8">
+        <v>74</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="3:11">
       <c r="C34" s="1">
         <v>1029</v>
       </c>
@@ -2051,13 +2350,22 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="3:8">
+        <v>76</v>
+      </c>
+      <c r="H34" s="1">
+        <v>2</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="3:11">
       <c r="C35" s="1">
         <v>1030</v>
       </c>
@@ -2071,13 +2379,22 @@
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="3:8">
+        <v>78</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="3:11">
       <c r="C36" s="1">
         <v>1031</v>
       </c>
@@ -2091,13 +2408,22 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="3:8">
+        <v>80</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="3:11">
       <c r="C37" s="1">
         <v>1032</v>
       </c>
@@ -2111,13 +2437,22 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="3:8">
+        <v>82</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="3:11">
       <c r="C38" s="1">
         <v>1033</v>
       </c>
@@ -2131,13 +2466,22 @@
         <v>2</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="3:8">
+        <v>84</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="3:11">
       <c r="C39" s="1">
         <v>1034</v>
       </c>
@@ -2151,13 +2495,22 @@
         <v>2</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="3:8">
+        <v>86</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="3:11">
       <c r="C40" s="1">
         <v>1035</v>
       </c>
@@ -2171,13 +2524,22 @@
         <v>2</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="3:8">
+        <v>88</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="3:11">
       <c r="C41" s="1">
         <v>1036</v>
       </c>
@@ -2191,13 +2553,22 @@
         <v>2</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="3:8">
+        <v>90</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="3:11">
       <c r="C42" s="1">
         <v>1037</v>
       </c>
@@ -2211,13 +2582,22 @@
         <v>2</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="3:8">
+        <v>92</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="3:11">
       <c r="C43" s="1">
         <v>1038</v>
       </c>
@@ -2231,13 +2611,22 @@
         <v>3</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="3:8">
+        <v>94</v>
+      </c>
+      <c r="H43" s="1">
+        <v>2</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="3:11">
       <c r="C44" s="1">
         <v>1039</v>
       </c>
@@ -2251,13 +2640,22 @@
         <v>3</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="3:8">
+        <v>96</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="3:11">
       <c r="C45" s="1">
         <v>1040</v>
       </c>
@@ -2271,13 +2669,22 @@
         <v>3</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="3:8">
+        <v>98</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="3:11">
       <c r="C46" s="1">
         <v>1041</v>
       </c>
@@ -2291,13 +2698,22 @@
         <v>3</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="3:8">
+        <v>100</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="3:11">
       <c r="C47" s="1">
         <v>1042</v>
       </c>
@@ -2311,13 +2727,22 @@
         <v>3</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="3:8">
+        <v>102</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="3:11">
       <c r="C48" s="1">
         <v>1043</v>
       </c>
@@ -2331,13 +2756,22 @@
         <v>3</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" spans="3:8">
+        <v>104</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="3:11">
       <c r="C49" s="1">
         <v>1044</v>
       </c>
@@ -2351,13 +2785,22 @@
         <v>3</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="3:8">
+        <v>106</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="3:11">
       <c r="C50" s="1">
         <v>1045</v>
       </c>
@@ -2371,13 +2814,22 @@
         <v>3</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="3:8">
+        <v>108</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="3:11">
       <c r="C51" s="1">
         <v>1046</v>
       </c>
@@ -2391,13 +2843,22 @@
         <v>3</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="3:8">
+        <v>110</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="3:11">
       <c r="C52" s="1">
         <v>1047</v>
       </c>
@@ -2411,13 +2872,22 @@
         <v>3</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="3:8">
+        <v>112</v>
+      </c>
+      <c r="H52" s="1">
+        <v>2</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="3:11">
       <c r="C53" s="1">
         <v>1048</v>
       </c>
@@ -2431,13 +2901,22 @@
         <v>4</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="3:8">
+        <v>114</v>
+      </c>
+      <c r="H53" s="1">
+        <v>3</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="3:11">
       <c r="C54" s="1">
         <v>1049</v>
       </c>
@@ -2451,13 +2930,22 @@
         <v>4</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="3:8">
+        <v>116</v>
+      </c>
+      <c r="H54" s="1">
+        <v>3</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="3:11">
       <c r="C55" s="1">
         <v>1050</v>
       </c>
@@ -2471,13 +2959,22 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="3:8">
+        <v>118</v>
+      </c>
+      <c r="H55" s="1">
+        <v>4</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="3:11">
       <c r="C56" s="1">
         <v>1051</v>
       </c>
@@ -2491,13 +2988,22 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="3:8">
+        <v>120</v>
+      </c>
+      <c r="H56" s="1">
+        <v>4</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="3:11">
       <c r="C57" s="1">
         <v>1052</v>
       </c>
@@ -2511,13 +3017,22 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" spans="3:8">
+        <v>122</v>
+      </c>
+      <c r="H57" s="1">
+        <v>4</v>
+      </c>
+      <c r="I57" s="1">
+        <v>1</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="3:11">
       <c r="C58" s="1">
         <v>1053</v>
       </c>
@@ -2531,13 +3046,22 @@
         <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="3:8">
+        <v>124</v>
+      </c>
+      <c r="H58" s="1">
+        <v>5</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="3:11">
       <c r="C59" s="1">
         <v>1054</v>
       </c>
@@ -2551,13 +3075,22 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" spans="3:8">
+        <v>126</v>
+      </c>
+      <c r="H59" s="1">
+        <v>5</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="3:11">
       <c r="C60" s="1">
         <v>1055</v>
       </c>
@@ -2571,13 +3104,22 @@
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" spans="3:8">
+        <v>128</v>
+      </c>
+      <c r="H60" s="1">
+        <v>5</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="3:11">
       <c r="C61" s="1">
         <v>1056</v>
       </c>
@@ -2591,10 +3133,19 @@
         <v>0</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
+      </c>
+      <c r="H61" s="1">
+        <v>5</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>23</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>25</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>27</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>29</v>
@@ -1692,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>31</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>33</v>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>35</v>
@@ -1779,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>37</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>39</v>
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>41</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>43</v>
@@ -1895,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>45</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>47</v>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>49</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>51</v>
@@ -2011,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>53</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>55</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>57</v>
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>59</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>61</v>
@@ -2156,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>63</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>65</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>67</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>69</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>71</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>73</v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>75</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>77</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>79</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>81</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>83</v>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>85</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>87</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>89</v>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>91</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>93</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>95</v>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>97</v>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>99</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>101</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>103</v>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>105</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>107</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>109</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>111</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>113</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>115</v>
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>117</v>
